--- a/StructureDefinition-VunsPneumoBioReport.xlsx
+++ b/StructureDefinition-VunsPneumoBioReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2289" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2280" uniqueCount="453">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -449,6 +449,189 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.identifier</t>
+  </si>
+  <si>
+    <t>ReportID
+Filler IDPlacer ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Business identifier for report</t>
+  </si>
+  <si>
+    <t>Identifiers assigned to this report by the performer or other systems.</t>
+  </si>
+  <si>
+    <t>Usually assigned by the Information System of the diagnostic service provider (filler id).</t>
+  </si>
+  <si>
+    <t>Need to know what identifier to use when making queries about this report from the source laboratory, and for linking to the report outside FHIR context.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>OBR-51/ for globally unique filler ID  - OBR-3 , For non-globally unique filler-id the flller/placer number must be combined with the universal service Id -  OBR-2(if present)+OBR-3+OBR-4</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+</t>
+  </si>
+  <si>
+    <t>What was requested</t>
+  </si>
+  <si>
+    <t>Details concerning a service requested.</t>
+  </si>
+  <si>
+    <t>Note: Usually there is one test request for each result, however in some circumstances multiple test requests may be represented using a single test result resource. Note that there are also cases where one request leads to multiple reports.</t>
+  </si>
+  <si>
+    <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
+  </si>
+  <si>
+    <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>ORC? OBR-2/3?</t>
+  </si>
+  <si>
+    <t>outboundRelationship[typeCode=FLFS].target</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.status</t>
+  </si>
+  <si>
+    <t>registered | partial | preliminary | final +</t>
+  </si>
+  <si>
+    <t>The status of the diagnostic report.</t>
+  </si>
+  <si>
+    <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
+  </si>
+  <si>
+    <t>final</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-report-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>OBR-25 (not 1:1 mapping)</t>
+  </si>
+  <si>
+    <t>statusCode  Note: final and amended are distinguished by whether observation is the subject of a ControlAct event of type "revise"</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
+</t>
+  </si>
+  <si>
+    <t>Concept - reference to a terminology or just  text</t>
+  </si>
+  <si>
+    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes for diagnostic service sections.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE</t>
+  </si>
+  <si>
+    <t>CD</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
@@ -459,200 +642,6 @@
     <t>open</t>
   </si>
   <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.identifier</t>
-  </si>
-  <si>
-    <t>ReportID
-Filler IDPlacer ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Business identifier for report</t>
-  </si>
-  <si>
-    <t>Identifiers assigned to this report by the performer or other systems.</t>
-  </si>
-  <si>
-    <t>Usually assigned by the Information System of the diagnostic service provider (filler id).</t>
-  </si>
-  <si>
-    <t>Need to know what identifier to use when making queries about this report from the source laboratory, and for linking to the report outside FHIR context.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>OBR-51/ for globally unique filler ID  - OBR-3 , For non-globally unique filler-id the flller/placer number must be combined with the universal service Id -  OBR-2(if present)+OBR-3+OBR-4</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
-</t>
-  </si>
-  <si>
-    <t>What was requested</t>
-  </si>
-  <si>
-    <t>Details concerning a service requested.</t>
-  </si>
-  <si>
-    <t>Note: Usually there is one test request for each result, however in some circumstances multiple test requests may be represented using a single test result resource. Note that there are also cases where one request leads to multiple reports.</t>
-  </si>
-  <si>
-    <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>ORC? OBR-2/3?</t>
-  </si>
-  <si>
-    <t>outboundRelationship[typeCode=FLFS].target</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.status</t>
-  </si>
-  <si>
-    <t>registered | partial | preliminary | final +</t>
-  </si>
-  <si>
-    <t>The status of the diagnostic report.</t>
-  </si>
-  <si>
-    <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
-  </si>
-  <si>
-    <t>final</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-report-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>OBR-25 (not 1:1 mapping)</t>
-  </si>
-  <si>
-    <t>statusCode  Note: final and amended are distinguished by whether observation is the subject of a ControlAct event of type "revise"</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category</t>
-  </si>
-  <si>
-    <t>Department
-Sub-departmentServiceDiscipline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
-</t>
-  </si>
-  <si>
-    <t>Concept - reference to a terminology or just  text</t>
-  </si>
-  <si>
-    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
-  </si>
-  <si>
-    <t>OBR-24</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -678,10 +667,10 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
   </si>
   <si>
     <t>DiagnosticReport.category.coding.id</t>
@@ -771,9 +760,6 @@
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
@@ -789,7 +775,19 @@
     <t>DiagnosticReport.category.coding.display.id</t>
   </si>
   <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
     <t>DiagnosticReport.category.coding.display.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>DiagnosticReport.category.coding.display.extension:translation</t>
@@ -817,6 +815,9 @@
     <t>Primitive value for string</t>
   </si>
   <si>
+    <t>The actual value</t>
+  </si>
+  <si>
     <t>1048576</t>
   </si>
   <si>
@@ -878,26 +879,10 @@
     <t>DiagnosticReport.code</t>
   </si>
   <si>
-    <t xml:space="preserve">Type
-</t>
-  </si>
-  <si>
     <t>Codes that describe Diagnostic Reports.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/report-codes</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>OBR-4 (HL7 v2 doesn't provide an easy way to indicate both the ordered test and the performed panel)</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
   </si>
   <si>
     <t>DiagnosticReport.code.id</t>
@@ -935,9 +920,6 @@
     <t>The subject of the report. Usually, but not always, this is a patient. However, diagnostic services also perform analyses on specimens collected from a variety of other sources.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>SHALL know the subject context.</t>
   </si>
   <si>
@@ -1021,9 +1003,6 @@
     <t>Reference.identifier</t>
   </si>
   <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
     <t>.identifier</t>
   </si>
   <si>
@@ -1455,10 +1434,6 @@
   </si>
   <si>
     <t>Gives laboratory the ability to provide its own fully formatted report for clinical fidelity.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
   </si>
   <si>
     <t>text (type=ED)</t>
@@ -2815,19 +2790,19 @@
         <v>19</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2839,7 +2814,7 @@
         <v>19</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>19</v>
@@ -2856,10 +2831,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2885,16 +2860,16 @@
         <v>135</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>138</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>19</v>
@@ -2931,19 +2906,19 @@
         <v>19</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2955,7 +2930,7 @@
         <v>19</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>19</v>
@@ -2972,14 +2947,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2998,19 +2973,19 @@
         <v>90</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>19</v>
@@ -3059,7 +3034,7 @@
         <v>19</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3068,34 +3043,34 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3114,19 +3089,19 @@
         <v>19</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O12" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>19</v>
@@ -3175,7 +3150,7 @@
         <v>19</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3184,19 +3159,19 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>19</v>
@@ -3204,10 +3179,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3233,21 +3208,21 @@
         <v>109</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>19</v>
@@ -3265,13 +3240,13 @@
         <v>19</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>19</v>
@@ -3289,7 +3264,7 @@
         <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>89</v>
@@ -3304,28 +3279,28 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>184</v>
+        <v>19</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3341,19 +3316,19 @@
         <v>19</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3379,13 +3354,13 @@
         <v>19</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>19</v>
@@ -3403,7 +3378,7 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3412,7 +3387,7 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>101</v>
@@ -3421,21 +3396,21 @@
         <v>19</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>194</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3458,13 +3433,13 @@
         <v>19</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3515,7 +3490,7 @@
         <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3536,7 +3511,7 @@
         <v>19</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>19</v>
@@ -3544,10 +3519,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3576,7 +3551,7 @@
         <v>136</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>138</v>
@@ -3617,19 +3592,19 @@
         <v>19</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3641,7 +3616,7 @@
         <v>19</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>19</v>
@@ -3650,7 +3625,7 @@
         <v>19</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>19</v>
@@ -3658,10 +3633,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3681,22 +3656,22 @@
         <v>19</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>19</v>
@@ -3745,7 +3720,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3754,7 +3729,7 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>101</v>
@@ -3763,10 +3738,10 @@
         <v>19</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>19</v>
@@ -3774,10 +3749,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3800,13 +3775,13 @@
         <v>19</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3857,7 +3832,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3878,7 +3853,7 @@
         <v>19</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>19</v>
@@ -3886,10 +3861,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3918,7 +3893,7 @@
         <v>136</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>138</v>
@@ -3959,19 +3934,19 @@
         <v>19</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3983,7 +3958,7 @@
         <v>19</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>19</v>
@@ -3992,7 +3967,7 @@
         <v>19</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>19</v>
@@ -4000,10 +3975,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4029,16 +4004,16 @@
         <v>103</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>19</v>
@@ -4048,7 +4023,7 @@
         <v>19</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>19</v>
@@ -4087,7 +4062,7 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4105,10 +4080,10 @@
         <v>19</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>19</v>
@@ -4116,10 +4091,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4142,16 +4117,16 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4201,7 +4176,7 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4219,10 +4194,10 @@
         <v>19</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>19</v>
@@ -4230,10 +4205,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4259,14 +4234,14 @@
         <v>109</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>19</v>
@@ -4276,7 +4251,7 @@
         <v>19</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>19</v>
@@ -4315,7 +4290,7 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4333,10 +4308,10 @@
         <v>19</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>19</v>
@@ -4344,10 +4319,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4370,19 +4345,17 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>19</v>
@@ -4431,7 +4404,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4449,10 +4422,10 @@
         <v>19</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>19</v>
@@ -4460,10 +4433,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4486,13 +4459,13 @@
         <v>19</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4543,7 +4516,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4564,7 +4537,7 @@
         <v>19</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>200</v>
+        <v>19</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>19</v>
@@ -4572,14 +4545,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4601,14 +4574,12 @@
         <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>136</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>19</v>
@@ -4645,19 +4616,17 @@
         <v>19</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4669,7 +4638,7 @@
         <v>19</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>19</v>
@@ -4678,7 +4647,7 @@
         <v>19</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>200</v>
+        <v>19</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>19</v>
@@ -4689,13 +4658,13 @@
         <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>250</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4722,9 +4691,7 @@
       <c r="M26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>19</v>
@@ -4773,7 +4740,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4782,10 +4749,10 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>19</v>
@@ -4828,13 +4795,13 @@
         <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>256</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4858,7 +4825,7 @@
         <v>19</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="X27" t="s" s="2">
         <v>19</v>
@@ -4885,7 +4852,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4914,10 +4881,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4940,19 +4907,19 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>19</v>
@@ -5001,7 +4968,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5019,10 +4986,10 @@
         <v>19</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>19</v>
@@ -5030,10 +4997,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5056,19 +5023,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>19</v>
@@ -5117,7 +5084,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5135,10 +5102,10 @@
         <v>19</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>19</v>
@@ -5146,14 +5113,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>277</v>
+        <v>19</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5169,19 +5136,19 @@
         <v>19</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5231,7 +5198,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>89</v>
@@ -5240,30 +5207,30 @@
         <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>280</v>
+        <v>19</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>281</v>
+        <v>187</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>282</v>
+        <v>188</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>283</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5286,13 +5253,13 @@
         <v>19</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5343,7 +5310,7 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5364,7 +5331,7 @@
         <v>19</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>19</v>
@@ -5372,10 +5339,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5404,7 +5371,7 @@
         <v>136</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>138</v>
@@ -5445,19 +5412,19 @@
         <v>19</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5469,7 +5436,7 @@
         <v>19</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>19</v>
@@ -5478,7 +5445,7 @@
         <v>19</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>19</v>
@@ -5486,10 +5453,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5509,22 +5476,22 @@
         <v>19</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>19</v>
@@ -5534,7 +5501,7 @@
         <v>19</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>19</v>
@@ -5573,7 +5540,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5582,7 +5549,7 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>101</v>
@@ -5591,10 +5558,10 @@
         <v>19</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>19</v>
@@ -5602,10 +5569,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5628,19 +5595,19 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>19</v>
@@ -5689,7 +5656,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5707,10 +5674,10 @@
         <v>19</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>19</v>
@@ -5718,14 +5685,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5744,19 +5711,17 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>19</v>
@@ -5805,7 +5770,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5814,30 +5779,30 @@
         <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5860,13 +5825,13 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5917,7 +5882,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5938,7 +5903,7 @@
         <v>19</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>19</v>
@@ -5946,10 +5911,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5978,7 +5943,7 @@
         <v>136</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>138</v>
@@ -6019,19 +5984,19 @@
         <v>19</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6043,7 +6008,7 @@
         <v>19</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>19</v>
@@ -6052,7 +6017,7 @@
         <v>19</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>19</v>
@@ -6060,10 +6025,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6086,16 +6051,16 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6145,7 +6110,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6154,7 +6119,7 @@
         <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
@@ -6174,10 +6139,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6203,13 +6168,13 @@
         <v>103</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6235,13 +6200,13 @@
         <v>19</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>19</v>
@@ -6259,7 +6224,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6288,10 +6253,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6314,16 +6279,16 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6373,7 +6338,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6382,7 +6347,7 @@
         <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>101</v>
@@ -6391,10 +6356,10 @@
         <v>19</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>321</v>
+        <v>19</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>19</v>
@@ -6402,10 +6367,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6428,16 +6393,16 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6487,7 +6452,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6516,14 +6481,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6542,19 +6507,19 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>19</v>
@@ -6603,7 +6568,7 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6612,34 +6577,34 @@
         <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6658,19 +6623,19 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>19</v>
@@ -6719,7 +6684,7 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6728,30 +6693,30 @@
         <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6774,13 +6739,13 @@
         <v>19</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6831,7 +6796,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6852,7 +6817,7 @@
         <v>19</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>19</v>
@@ -6860,10 +6825,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6892,7 +6857,7 @@
         <v>136</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>138</v>
@@ -6933,19 +6898,19 @@
         <v>19</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6954,10 +6919,10 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>19</v>
@@ -6966,7 +6931,7 @@
         <v>19</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>132</v>
+        <v>194</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>19</v>
@@ -6974,16 +6939,16 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7002,17 +6967,15 @@
         <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>19</v>
@@ -7061,7 +7024,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7070,10 +7033,10 @@
         <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>19</v>
@@ -7082,7 +7045,7 @@
         <v>19</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>19</v>
@@ -7090,14 +7053,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7116,19 +7079,19 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -7177,7 +7140,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7195,25 +7158,25 @@
         <v>19</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7232,19 +7195,19 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -7293,7 +7256,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7302,34 +7265,34 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7348,19 +7311,19 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -7409,7 +7372,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7418,30 +7381,30 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7464,19 +7427,19 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -7525,7 +7488,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7534,19 +7497,19 @@
         <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>19</v>
@@ -7554,14 +7517,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7580,19 +7543,19 @@
         <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>19</v>
@@ -7629,17 +7592,17 @@
         <v>19</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7648,19 +7611,19 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>19</v>
@@ -7668,16 +7631,16 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7696,19 +7659,19 @@
         <v>19</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -7757,7 +7720,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7766,19 +7729,19 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>19</v>
@@ -7786,10 +7749,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7812,16 +7775,16 @@
         <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7871,7 +7834,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7880,10 +7843,10 @@
         <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>19</v>
@@ -7892,7 +7855,7 @@
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>19</v>
@@ -7900,14 +7863,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7926,17 +7889,17 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>19</v>
@@ -7985,7 +7948,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7994,7 +7957,7 @@
         <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>101</v>
@@ -8003,10 +7966,10 @@
         <v>19</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>19</v>
@@ -8014,10 +7977,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8040,13 +8003,13 @@
         <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8097,7 +8060,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8118,7 +8081,7 @@
         <v>19</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>19</v>
@@ -8126,10 +8089,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8158,7 +8121,7 @@
         <v>136</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>138</v>
@@ -8199,19 +8162,19 @@
         <v>19</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8223,7 +8186,7 @@
         <v>19</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>19</v>
@@ -8232,7 +8195,7 @@
         <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>19</v>
@@ -8240,14 +8203,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8269,16 +8232,16 @@
         <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>138</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>19</v>
@@ -8327,7 +8290,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8339,7 +8302,7 @@
         <v>19</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>19</v>
@@ -8356,10 +8319,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8382,19 +8345,19 @@
         <v>19</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>19</v>
@@ -8443,7 +8406,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8464,7 +8427,7 @@
         <v>19</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>19</v>
@@ -8472,10 +8435,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8498,17 +8461,15 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -8557,7 +8518,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>89</v>
@@ -8566,10 +8527,10 @@
         <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>19</v>
@@ -8578,7 +8539,7 @@
         <v>19</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>19</v>
@@ -8586,14 +8547,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8612,19 +8573,17 @@
         <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>19</v>
@@ -8673,7 +8632,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8691,10 +8650,10 @@
         <v>19</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>19</v>
@@ -8702,10 +8661,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8728,17 +8687,15 @@
         <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>19</v>
@@ -8763,13 +8720,13 @@
         <v>19</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>19</v>
@@ -8787,7 +8744,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8796,7 +8753,7 @@
         <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>101</v>
@@ -8805,10 +8762,10 @@
         <v>19</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>19</v>
@@ -8816,10 +8773,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8842,19 +8799,19 @@
         <v>19</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>19</v>
@@ -8903,7 +8860,7 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8912,19 +8869,19 @@
         <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>458</v>
+        <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>19</v>

--- a/StructureDefinition-VunsPneumoBioReport.xlsx
+++ b/StructureDefinition-VunsPneumoBioReport.xlsx
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil pour un rapport de biologies d'intérêt pneumologique</t>
+    <t>Profile for significant laboratory reports in the scope of chronic respiratory disease remote monitoring</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-VunsPneumoBioReport.xlsx
+++ b/StructureDefinition-VunsPneumoBioReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-VunsPneumoBioReport.xlsx
+++ b/StructureDefinition-VunsPneumoBioReport.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>RM@H IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
+    <t>VUNS IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
   </si>
   <si>
     <t>FHIR Version</t>
